--- a/docs/datos-prueba/insumos.xlsx
+++ b/docs/datos-prueba/insumos.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:C31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -409,9 +409,6 @@
       <c r="C1" t="str">
         <v>grupo</v>
       </c>
-      <c r="D1" t="str">
-        <v>valorUnitario</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -421,10 +418,7 @@
         <v>bulto</v>
       </c>
       <c r="C2" t="str">
-        <v>MATERIALES</v>
-      </c>
-      <c r="D2">
-        <v>34500</v>
+        <v>MATERIAL</v>
       </c>
     </row>
     <row r="3">
@@ -435,10 +429,7 @@
         <v>m3</v>
       </c>
       <c r="C3" t="str">
-        <v>MATERIALES</v>
-      </c>
-      <c r="D3">
-        <v>95000</v>
+        <v>MATERIAL</v>
       </c>
     </row>
     <row r="4">
@@ -449,10 +440,7 @@
         <v>m3</v>
       </c>
       <c r="C4" t="str">
-        <v>MATERIALES</v>
-      </c>
-      <c r="D4">
-        <v>118000</v>
+        <v>MATERIAL</v>
       </c>
     </row>
     <row r="5">
@@ -463,10 +451,7 @@
         <v>und</v>
       </c>
       <c r="C5" t="str">
-        <v>MATERIALES</v>
-      </c>
-      <c r="D5">
-        <v>2450</v>
+        <v>MATERIAL</v>
       </c>
     </row>
     <row r="6">
@@ -477,10 +462,7 @@
         <v>und</v>
       </c>
       <c r="C6" t="str">
-        <v>MATERIALES</v>
-      </c>
-      <c r="D6">
-        <v>1150</v>
+        <v>MATERIAL</v>
       </c>
     </row>
     <row r="7">
@@ -491,10 +473,7 @@
         <v>kg</v>
       </c>
       <c r="C7" t="str">
-        <v>MATERIALES</v>
-      </c>
-      <c r="D7">
-        <v>5800</v>
+        <v>MATERIAL</v>
       </c>
     </row>
     <row r="8">
@@ -505,10 +484,7 @@
         <v>kg</v>
       </c>
       <c r="C8" t="str">
-        <v>MATERIALES</v>
-      </c>
-      <c r="D8">
-        <v>7200</v>
+        <v>MATERIAL</v>
       </c>
     </row>
     <row r="9">
@@ -519,10 +495,7 @@
         <v>m2</v>
       </c>
       <c r="C9" t="str">
-        <v>MATERIALES</v>
-      </c>
-      <c r="D9">
-        <v>62000</v>
+        <v>MATERIAL</v>
       </c>
     </row>
     <row r="10">
@@ -533,10 +506,7 @@
         <v>m2</v>
       </c>
       <c r="C10" t="str">
-        <v>MATERIALES</v>
-      </c>
-      <c r="D10">
-        <v>38500</v>
+        <v>MATERIAL</v>
       </c>
     </row>
     <row r="11">
@@ -547,10 +517,7 @@
         <v>bulto</v>
       </c>
       <c r="C11" t="str">
-        <v>MATERIALES</v>
-      </c>
-      <c r="D11">
-        <v>42000</v>
+        <v>MATERIAL</v>
       </c>
     </row>
     <row r="12">
@@ -561,10 +528,7 @@
         <v>kg</v>
       </c>
       <c r="C12" t="str">
-        <v>MATERIALES</v>
-      </c>
-      <c r="D12">
-        <v>9800</v>
+        <v>MATERIAL</v>
       </c>
     </row>
     <row r="13">
@@ -575,10 +539,7 @@
         <v>galón</v>
       </c>
       <c r="C13" t="str">
-        <v>MATERIALES</v>
-      </c>
-      <c r="D13">
-        <v>38000</v>
+        <v>MATERIAL</v>
       </c>
     </row>
     <row r="14">
@@ -589,10 +550,7 @@
         <v>galón</v>
       </c>
       <c r="C14" t="str">
-        <v>MATERIALES</v>
-      </c>
-      <c r="D14">
-        <v>89000</v>
+        <v>MATERIAL</v>
       </c>
     </row>
     <row r="15">
@@ -603,10 +561,7 @@
         <v>ml</v>
       </c>
       <c r="C15" t="str">
-        <v>MATERIALES</v>
-      </c>
-      <c r="D15">
-        <v>12400</v>
+        <v>MATERIAL</v>
       </c>
     </row>
     <row r="16">
@@ -617,10 +572,7 @@
         <v>ml</v>
       </c>
       <c r="C16" t="str">
-        <v>MATERIALES</v>
-      </c>
-      <c r="D16">
-        <v>28500</v>
+        <v>MATERIAL</v>
       </c>
     </row>
     <row r="17">
@@ -631,10 +583,7 @@
         <v>ml</v>
       </c>
       <c r="C17" t="str">
-        <v>MATERIALES</v>
-      </c>
-      <c r="D17">
-        <v>3900</v>
+        <v>MATERIAL</v>
       </c>
     </row>
     <row r="18">
@@ -645,10 +594,7 @@
         <v>und</v>
       </c>
       <c r="C18" t="str">
-        <v>MATERIALES</v>
-      </c>
-      <c r="D18">
-        <v>12800</v>
+        <v>MATERIAL</v>
       </c>
     </row>
     <row r="19">
@@ -659,10 +605,7 @@
         <v>kg</v>
       </c>
       <c r="C19" t="str">
-        <v>MATERIALES</v>
-      </c>
-      <c r="D19">
-        <v>8600</v>
+        <v>MATERIAL</v>
       </c>
     </row>
     <row r="20">
@@ -675,9 +618,6 @@
       <c r="C20" t="str">
         <v>MANO_OBRA</v>
       </c>
-      <c r="D20">
-        <v>98000</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
@@ -689,9 +629,6 @@
       <c r="C21" t="str">
         <v>MANO_OBRA</v>
       </c>
-      <c r="D21">
-        <v>68000</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
@@ -703,9 +640,6 @@
       <c r="C22" t="str">
         <v>MANO_OBRA</v>
       </c>
-      <c r="D22">
-        <v>145000</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
@@ -717,9 +651,6 @@
       <c r="C23" t="str">
         <v>MANO_OBRA</v>
       </c>
-      <c r="D23">
-        <v>115000</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
@@ -731,9 +662,6 @@
       <c r="C24" t="str">
         <v>MANO_OBRA</v>
       </c>
-      <c r="D24">
-        <v>92000</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
@@ -745,9 +673,6 @@
       <c r="C25" t="str">
         <v>MANO_OBRA</v>
       </c>
-      <c r="D25">
-        <v>125000</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
@@ -757,10 +682,7 @@
         <v>día</v>
       </c>
       <c r="C26" t="str">
-        <v>EQUIPOS</v>
-      </c>
-      <c r="D26">
-        <v>85000</v>
+        <v>EQUIPO</v>
       </c>
     </row>
     <row r="27">
@@ -771,10 +693,7 @@
         <v>día</v>
       </c>
       <c r="C27" t="str">
-        <v>EQUIPOS</v>
-      </c>
-      <c r="D27">
-        <v>18000</v>
+        <v>EQUIPO</v>
       </c>
     </row>
     <row r="28">
@@ -785,10 +704,7 @@
         <v>día</v>
       </c>
       <c r="C28" t="str">
-        <v>EQUIPOS</v>
-      </c>
-      <c r="D28">
-        <v>32000</v>
+        <v>EQUIPO</v>
       </c>
     </row>
     <row r="29">
@@ -799,10 +715,7 @@
         <v>global</v>
       </c>
       <c r="C29" t="str">
-        <v>EQUIPOS</v>
-      </c>
-      <c r="D29">
-        <v>5500</v>
+        <v>EQUIPO</v>
       </c>
     </row>
     <row r="30">
@@ -815,9 +728,6 @@
       <c r="C30" t="str">
         <v>TRANSPORTE</v>
       </c>
-      <c r="D30">
-        <v>180000</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
@@ -829,13 +739,10 @@
       <c r="C31" t="str">
         <v>TRANSPORTE</v>
       </c>
-      <c r="D31">
-        <v>22000</v>
-      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C31"/>
   </ignoredErrors>
 </worksheet>
 </file>